--- a/TextGame project/Assets/Resources/Story/12.xlsx
+++ b/TextGame project/Assets/Resources/Story/12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2340DC2A-F3DB-4E0D-80F2-4965AB451DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B333464E-2F60-497D-8A9D-DBB941A94B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="96">
   <si>
     <t>Name</t>
   </si>
@@ -113,9 +113,6 @@
     <t>林深</t>
   </si>
   <si>
-    <t>跑！</t>
-  </si>
-  <si>
     <t>Linshen</t>
   </si>
   <si>
@@ -125,48 +122,24 @@
     <t>王叔叔</t>
   </si>
   <si>
-    <t>就凭你？</t>
-  </si>
-  <si>
     <t>（两人扭打在一起）</t>
   </si>
   <si>
     <t>千叶</t>
   </si>
   <si>
-    <t>林深！</t>
-  </si>
-  <si>
     <t>Qianye</t>
   </si>
   <si>
-    <t>快跑啊！</t>
-  </si>
-  <si>
     <t>（王叔叔一棍子打在林深的胳膊上）</t>
   </si>
   <si>
-    <t>呃...</t>
-  </si>
-  <si>
-    <t>走啊！快去报警！</t>
-  </si>
-  <si>
     <t>（他用力推开王叔叔，把他往密室里引）</t>
   </si>
   <si>
-    <t>快走！别回头！</t>
-  </si>
-  <si>
     <t>（千叶看着林深，眼泪模糊了视线）</t>
   </si>
   <si>
-    <t>林深...</t>
-  </si>
-  <si>
-    <t>走！</t>
-  </si>
-  <si>
     <t>（千叶咬了咬牙，转身跑了）</t>
   </si>
   <si>
@@ -185,9 +158,6 @@
     <t>（她颤抖着拿出手机，拨通了 110）</t>
   </si>
   <si>
-    <t>喂... 警察吗... 救命... 废弃学校... 有人... 杀人魔...</t>
-  </si>
-  <si>
     <t>（警察很快来了，冲进了学校）</t>
   </si>
   <si>
@@ -209,36 +179,12 @@
     <t>警察</t>
   </si>
   <si>
-    <t>小姑娘，别怕，没事了。</t>
-  </si>
-  <si>
     <t>Police</t>
   </si>
   <si>
-    <t>警察叔叔... 还有一个人... 一个男生... 他怎么样了？</t>
-  </si>
-  <si>
-    <t>我们进去的时候，里面只有他一个人。没看到其他的人。</t>
-  </si>
-  <si>
-    <t>什么...？</t>
-  </si>
-  <si>
-    <t>你说的那个男生，长什么样？</t>
-  </si>
-  <si>
-    <t>他叫林深，穿着深色的衣服，个子高高的... 他说他是侦探...</t>
-  </si>
-  <si>
     <t>（警察查了查）</t>
   </si>
   <si>
-    <t>没有这个人的记录。而且... 我们在里面也没找到其他人。</t>
-  </si>
-  <si>
-    <t>怎么会... 他明明在里面的...</t>
-  </si>
-  <si>
     <t>（她冲进学校，跑到钟楼）</t>
   </si>
   <si>
@@ -251,9 +197,6 @@
     <t>（就像... 凭空消失了一样）</t>
   </si>
   <si>
-    <t>林深！林深你在哪儿！</t>
-  </si>
-  <si>
     <t>（没有人回答）</t>
   </si>
   <si>
@@ -278,9 +221,6 @@
     <t>（但是... 那个沉默寡言的侦探，却不见了）</t>
   </si>
   <si>
-    <t>林深... 你到底去哪儿了...</t>
-  </si>
-  <si>
     <t>（风吹过，卷起地上的落叶）</t>
   </si>
   <si>
@@ -293,13 +233,7 @@
     <t>（她把玩偶抱在怀里，轻声说）</t>
   </si>
   <si>
-    <t>谢谢你，林深。</t>
-  </si>
-  <si>
     <t>（她抬起头，看着夕阳）</t>
-  </si>
-  <si>
-    <t>我会找到你的。</t>
   </si>
   <si>
     <t>appearAt</t>
@@ -320,6 +254,98 @@
   </si>
   <si>
     <t>Yifan</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（挡在千叶前面，低声说）跑！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷笑）就凭你？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（站在原地，不知所措）林深！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（边打边喊）快跑啊！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（闷哼一声）呃...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（哭着喊）林深！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（咬着牙，对她喊）走啊！快去报警！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（对千叶喊）快走！别回头！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（哭着）林深...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（大喊）走！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（哭着，语无伦次）喂... 警察吗... 救命... 废弃学校... 有人... 杀人魔...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（温和）小姑娘，别怕，没事了。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（抓住警察的胳膊，着急地问）警察叔叔... 还有一个人... 一个男生... 他怎么样了？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（摇头）我们进去的时候，里面只有他一个人。没看到其他的人。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（愣住）什么...？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（疑惑）你说的那个男生，长什么样？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（着急）他叫林深，穿着深色的衣服，个子高高的... 他说他是侦探...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（摇头）没有这个人的记录。而且... 我们在里面也没找到其他人。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（不敢相信）怎么会... 他明明在里面的...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（喊着）林深！林深你在哪儿！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（喃喃）林深... 你到底去哪儿了...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（轻声）谢谢你，林深。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（坚定）我会找到你的。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -970,7 +996,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="G2" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -989,35 +1015,38 @@
       <c r="E3">
         <v>8</v>
       </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="J3" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="M3" s="1">
         <v>819.16989999999998</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="P3" s="1">
         <v>570</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1025,13 +1054,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
       <c r="R4">
         <v>8</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -1048,13 +1080,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="R5">
         <v>8</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -1068,16 +1103,19 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="R6">
         <v>8</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -1094,13 +1132,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="R7">
         <v>8</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -1114,16 +1155,19 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R8">
         <v>8</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -1140,13 +1184,16 @@
         <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9">
         <v>8</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
       </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
@@ -1163,13 +1210,16 @@
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
       </c>
       <c r="R10">
         <v>8</v>
+      </c>
+      <c r="S10">
+        <v>3</v>
       </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
@@ -1186,13 +1236,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R11">
         <v>8</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
       </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
@@ -1206,16 +1259,19 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R12">
         <v>8</v>
+      </c>
+      <c r="S12">
+        <v>3</v>
       </c>
       <c r="T12" s="1">
         <v>-640.83010000000002</v>
@@ -1232,13 +1288,16 @@
         <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R13">
         <v>8</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
       </c>
       <c r="T13" s="1">
         <v>-640.83010000000002</v>
@@ -1255,13 +1314,16 @@
         <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
       <c r="R14">
         <v>8</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
       </c>
       <c r="T14" s="1">
         <v>-640.83010000000002</v>
@@ -1278,13 +1340,16 @@
         <v>25</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R15">
         <v>8</v>
+      </c>
+      <c r="S15">
+        <v>3</v>
       </c>
       <c r="T15" s="1">
         <v>-640.83010000000002</v>
@@ -1301,13 +1366,16 @@
         <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="R16">
         <v>8</v>
+      </c>
+      <c r="S16">
+        <v>3</v>
       </c>
       <c r="T16" s="1">
         <v>-640.83010000000002</v>
@@ -1321,16 +1389,19 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R17">
         <v>8</v>
+      </c>
+      <c r="S17">
+        <v>3</v>
       </c>
       <c r="T17" s="1">
         <v>-640.83010000000002</v>
@@ -1347,13 +1418,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R18">
         <v>8</v>
+      </c>
+      <c r="S18">
+        <v>3</v>
       </c>
       <c r="T18" s="1">
         <v>-640.83010000000002</v>
@@ -1370,19 +1444,22 @@
         <v>22</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="R19">
         <v>8</v>
+      </c>
+      <c r="S19">
+        <v>3</v>
       </c>
       <c r="T19" s="1">
         <v>-640.83010000000002</v>
@@ -1399,13 +1476,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
       </c>
       <c r="R20">
         <v>8</v>
+      </c>
+      <c r="S20">
+        <v>3</v>
       </c>
       <c r="T20" s="1">
         <v>-640.83010000000002</v>
@@ -1422,13 +1502,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
       </c>
       <c r="R21">
         <v>8</v>
+      </c>
+      <c r="S21">
+        <v>3</v>
       </c>
       <c r="T21" s="1">
         <v>-640.83010000000002</v>
@@ -1445,13 +1528,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
       </c>
       <c r="R22">
         <v>8</v>
+      </c>
+      <c r="S22">
+        <v>3</v>
       </c>
       <c r="T22" s="1">
         <v>-640.83010000000002</v>
@@ -1468,13 +1554,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
       </c>
       <c r="R23">
         <v>8</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
       </c>
       <c r="T23" s="1">
         <v>-640.83010000000002</v>
@@ -1491,13 +1580,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
       </c>
       <c r="R24">
         <v>8</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
       </c>
       <c r="T24" s="1">
         <v>-640.83010000000002</v>
@@ -1511,16 +1603,19 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R25">
         <v>8</v>
+      </c>
+      <c r="S25">
+        <v>3</v>
       </c>
       <c r="T25" s="1">
         <v>-640.83010000000002</v>
@@ -1537,7 +1632,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
@@ -1545,8 +1640,14 @@
       <c r="E26">
         <v>3</v>
       </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
       <c r="R26">
         <v>8</v>
+      </c>
+      <c r="S26">
+        <v>3</v>
       </c>
       <c r="T26" s="1">
         <v>-640.83010000000002</v>
@@ -1563,13 +1664,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
       <c r="R27">
         <v>3</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
       </c>
       <c r="T27" s="1">
         <v>-640.83010000000002</v>
@@ -1586,31 +1690,34 @@
         <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="M28" s="1">
         <v>819.16989999999998</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="P28" s="1">
         <v>570</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="R28">
         <v>3</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
       </c>
       <c r="T28" s="1">
         <v>-640.83010000000002</v>
@@ -1627,13 +1734,16 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>24</v>
       </c>
       <c r="R29">
         <v>3</v>
+      </c>
+      <c r="S29">
+        <v>1</v>
       </c>
       <c r="T29" s="1">
         <v>-640.83010000000002</v>
@@ -1650,13 +1760,16 @@
         <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
       </c>
       <c r="R30">
         <v>3</v>
+      </c>
+      <c r="S30">
+        <v>1</v>
       </c>
       <c r="T30" s="1">
         <v>-640.83010000000002</v>
@@ -1673,16 +1786,19 @@
         <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="R31">
         <v>3</v>
+      </c>
+      <c r="S31">
+        <v>1</v>
       </c>
       <c r="T31" s="1">
         <v>-640.83010000000002</v>
@@ -1696,16 +1812,19 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="R32">
         <v>3</v>
+      </c>
+      <c r="S32">
+        <v>1</v>
       </c>
       <c r="T32" s="1">
         <v>-640.83010000000002</v>
@@ -1719,16 +1838,19 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R33">
         <v>3</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
       </c>
       <c r="T33" s="1">
         <v>-640.83010000000002</v>
@@ -1742,16 +1864,19 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="R34">
         <v>3</v>
+      </c>
+      <c r="S34">
+        <v>1</v>
       </c>
       <c r="T34" s="1">
         <v>-640.83010000000002</v>
@@ -1765,16 +1890,19 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R35">
         <v>3</v>
+      </c>
+      <c r="S35">
+        <v>1</v>
       </c>
       <c r="T35" s="1">
         <v>-640.83010000000002</v>
@@ -1788,16 +1916,19 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="R36">
         <v>3</v>
+      </c>
+      <c r="S36">
+        <v>1</v>
       </c>
       <c r="T36" s="1">
         <v>-640.83010000000002</v>
@@ -1811,16 +1942,19 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R37">
         <v>3</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
       </c>
       <c r="T37" s="1">
         <v>-640.83010000000002</v>
@@ -1837,13 +1971,16 @@
         <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
         <v>24</v>
       </c>
       <c r="R38">
         <v>3</v>
+      </c>
+      <c r="S38">
+        <v>1</v>
       </c>
       <c r="T38" s="1">
         <v>-640.83010000000002</v>
@@ -1857,16 +1994,19 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="R39">
         <v>3</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
       </c>
       <c r="T39" s="1">
         <v>-640.83010000000002</v>
@@ -1880,16 +2020,19 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R40">
         <v>3</v>
+      </c>
+      <c r="S40">
+        <v>1</v>
       </c>
       <c r="T40" s="1">
         <v>-640.83010000000002</v>
@@ -1906,16 +2049,22 @@
         <v>22</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="R41">
         <v>3</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
       </c>
       <c r="T41" s="1">
         <v>-640.83010000000002</v>
@@ -1932,13 +2081,16 @@
         <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S42">
+        <v>1</v>
       </c>
       <c r="T42" s="1">
         <v>-640.83010000000002</v>
@@ -1955,13 +2107,16 @@
         <v>22</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S43">
+        <v>1</v>
       </c>
       <c r="T43" s="1">
         <v>-640.83010000000002</v>
@@ -1978,13 +2133,16 @@
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
         <v>24</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S44">
+        <v>1</v>
       </c>
       <c r="T44" s="1">
         <v>-640.83010000000002</v>
@@ -1998,16 +2156,19 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R45">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S45">
+        <v>1</v>
       </c>
       <c r="T45" s="1">
         <v>-640.83010000000002</v>
@@ -2024,13 +2185,16 @@
         <v>22</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
         <v>24</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S46">
+        <v>1</v>
       </c>
       <c r="T46" s="1">
         <v>-640.83010000000002</v>
@@ -2047,13 +2211,16 @@
         <v>22</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
         <v>24</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S47">
+        <v>1</v>
       </c>
       <c r="T47" s="1">
         <v>-640.83010000000002</v>
@@ -2070,13 +2237,16 @@
         <v>22</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
         <v>24</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S48">
+        <v>1</v>
       </c>
       <c r="T48" s="1">
         <v>-640.83010000000002</v>
@@ -2093,13 +2263,19 @@
         <v>22</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
         <v>24</v>
       </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
       <c r="R49">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="S49">
+        <v>1</v>
       </c>
       <c r="T49" s="1">
         <v>-640.83010000000002</v>
@@ -2116,13 +2292,16 @@
         <v>22</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
         <v>24</v>
       </c>
       <c r="R50">
         <v>3</v>
+      </c>
+      <c r="S50">
+        <v>1</v>
       </c>
       <c r="T50" s="1">
         <v>-640.83010000000002</v>
@@ -2139,13 +2318,16 @@
         <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
         <v>24</v>
       </c>
       <c r="R51">
         <v>3</v>
+      </c>
+      <c r="S51">
+        <v>1</v>
       </c>
       <c r="T51" s="1">
         <v>-640.83010000000002</v>
@@ -2162,13 +2344,16 @@
         <v>22</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
         <v>24</v>
       </c>
       <c r="R52">
         <v>3</v>
+      </c>
+      <c r="S52">
+        <v>1</v>
       </c>
       <c r="T52" s="1">
         <v>-640.83010000000002</v>
@@ -2185,13 +2370,16 @@
         <v>22</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
       </c>
       <c r="R53">
         <v>3</v>
+      </c>
+      <c r="S53">
+        <v>1</v>
       </c>
       <c r="T53" s="1">
         <v>-640.83010000000002</v>
@@ -2205,16 +2393,19 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R54">
         <v>3</v>
+      </c>
+      <c r="S54">
+        <v>1</v>
       </c>
       <c r="T54" s="1">
         <v>-640.83010000000002</v>
@@ -2231,13 +2422,16 @@
         <v>22</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
         <v>24</v>
       </c>
       <c r="R55">
         <v>3</v>
+      </c>
+      <c r="S55">
+        <v>1</v>
       </c>
       <c r="T55" s="1">
         <v>-640.83010000000002</v>
@@ -2254,13 +2448,16 @@
         <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
       </c>
       <c r="R56">
         <v>3</v>
+      </c>
+      <c r="S56">
+        <v>1</v>
       </c>
       <c r="T56" s="1">
         <v>-640.83010000000002</v>
@@ -2277,13 +2474,16 @@
         <v>22</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
         <v>24</v>
       </c>
       <c r="R57">
         <v>3</v>
+      </c>
+      <c r="S57">
+        <v>1</v>
       </c>
       <c r="T57" s="1">
         <v>-640.83010000000002</v>
@@ -2300,13 +2500,16 @@
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
         <v>24</v>
       </c>
       <c r="R58">
         <v>3</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
       </c>
       <c r="T58" s="1">
         <v>-640.83010000000002</v>
@@ -2320,16 +2523,19 @@
     </row>
     <row r="59" spans="1:22">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R59">
         <v>3</v>
+      </c>
+      <c r="S59">
+        <v>1</v>
       </c>
       <c r="T59" s="1">
         <v>-640.83010000000002</v>
@@ -2346,13 +2552,16 @@
         <v>22</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
         <v>24</v>
       </c>
       <c r="R60">
         <v>3</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
       </c>
       <c r="T60" s="1">
         <v>-640.83010000000002</v>
@@ -2366,22 +2575,25 @@
     </row>
     <row r="61" spans="1:22">
       <c r="A61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E61">
         <v>9</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="R61">
         <v>3</v>
+      </c>
+      <c r="S61">
+        <v>1</v>
       </c>
       <c r="T61" s="1">
         <v>-640.83010000000002</v>
@@ -2396,55 +2608,73 @@
     <row r="62" spans="1:22">
       <c r="B62" s="2"/>
       <c r="G62" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H62">
         <v>11</v>
       </c>
+      <c r="S62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:22">
       <c r="G63" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H63">
         <v>12</v>
       </c>
+      <c r="S63">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:22">
       <c r="G64" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H64">
         <v>13</v>
       </c>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="S64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
       <c r="G65" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H65">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="S65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
       <c r="G66" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H66">
         <v>15</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="S66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
       <c r="G67" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H67">
         <v>16</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="S67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" s="7" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/TextGame project/Assets/Resources/Story/12.xlsx
+++ b/TextGame project/Assets/Resources/Story/12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B333464E-2F60-497D-8A9D-DBB941A94B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4188D1FF-1A03-4D1F-8C85-F94053296ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1641,7 +1641,7 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -1673,7 +1673,7 @@
         <v>3</v>
       </c>
       <c r="S27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T27" s="1">
         <v>-640.83010000000002</v>
@@ -1717,7 +1717,7 @@
         <v>3</v>
       </c>
       <c r="S28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T28" s="1">
         <v>-640.83010000000002</v>
@@ -1743,7 +1743,7 @@
         <v>3</v>
       </c>
       <c r="S29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T29" s="1">
         <v>-640.83010000000002</v>
@@ -1769,7 +1769,7 @@
         <v>3</v>
       </c>
       <c r="S30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T30" s="1">
         <v>-640.83010000000002</v>
@@ -1798,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T31" s="1">
         <v>-640.83010000000002</v>
@@ -1824,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="S32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T32" s="1">
         <v>-640.83010000000002</v>
@@ -1850,7 +1850,7 @@
         <v>3</v>
       </c>
       <c r="S33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T33" s="1">
         <v>-640.83010000000002</v>
@@ -1876,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T34" s="1">
         <v>-640.83010000000002</v>
@@ -1902,7 +1902,7 @@
         <v>3</v>
       </c>
       <c r="S35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T35" s="1">
         <v>-640.83010000000002</v>
@@ -1928,7 +1928,7 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T36" s="1">
         <v>-640.83010000000002</v>
@@ -1954,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="S37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T37" s="1">
         <v>-640.83010000000002</v>
@@ -1980,7 +1980,7 @@
         <v>3</v>
       </c>
       <c r="S38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T38" s="1">
         <v>-640.83010000000002</v>
@@ -2006,7 +2006,7 @@
         <v>3</v>
       </c>
       <c r="S39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T39" s="1">
         <v>-640.83010000000002</v>
@@ -2032,7 +2032,7 @@
         <v>3</v>
       </c>
       <c r="S40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T40" s="1">
         <v>-640.83010000000002</v>
@@ -2064,7 +2064,7 @@
         <v>3</v>
       </c>
       <c r="S41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T41" s="1">
         <v>-640.83010000000002</v>
@@ -2090,7 +2090,7 @@
         <v>8</v>
       </c>
       <c r="S42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T42" s="1">
         <v>-640.83010000000002</v>
@@ -2116,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="S43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T43" s="1">
         <v>-640.83010000000002</v>
@@ -2142,7 +2142,7 @@
         <v>8</v>
       </c>
       <c r="S44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T44" s="1">
         <v>-640.83010000000002</v>
@@ -2168,7 +2168,7 @@
         <v>8</v>
       </c>
       <c r="S45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T45" s="1">
         <v>-640.83010000000002</v>
@@ -2194,7 +2194,7 @@
         <v>8</v>
       </c>
       <c r="S46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T46" s="1">
         <v>-640.83010000000002</v>
@@ -2220,7 +2220,7 @@
         <v>8</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T47" s="1">
         <v>-640.83010000000002</v>
@@ -2246,7 +2246,7 @@
         <v>8</v>
       </c>
       <c r="S48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T48" s="1">
         <v>-640.83010000000002</v>
@@ -2275,7 +2275,7 @@
         <v>8</v>
       </c>
       <c r="S49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T49" s="1">
         <v>-640.83010000000002</v>
@@ -2301,7 +2301,7 @@
         <v>3</v>
       </c>
       <c r="S50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T50" s="1">
         <v>-640.83010000000002</v>
@@ -2327,7 +2327,7 @@
         <v>3</v>
       </c>
       <c r="S51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T51" s="1">
         <v>-640.83010000000002</v>
@@ -2353,7 +2353,7 @@
         <v>3</v>
       </c>
       <c r="S52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T52" s="1">
         <v>-640.83010000000002</v>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="S53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T53" s="1">
         <v>-640.83010000000002</v>
@@ -2405,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="S54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T54" s="1">
         <v>-640.83010000000002</v>
@@ -2431,7 +2431,7 @@
         <v>3</v>
       </c>
       <c r="S55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T55" s="1">
         <v>-640.83010000000002</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="S56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T56" s="1">
         <v>-640.83010000000002</v>
@@ -2483,7 +2483,7 @@
         <v>3</v>
       </c>
       <c r="S57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T57" s="1">
         <v>-640.83010000000002</v>
@@ -2509,7 +2509,7 @@
         <v>3</v>
       </c>
       <c r="S58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T58" s="1">
         <v>-640.83010000000002</v>
@@ -2535,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="S59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T59" s="1">
         <v>-640.83010000000002</v>
@@ -2561,7 +2561,7 @@
         <v>3</v>
       </c>
       <c r="S60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" s="1">
         <v>-640.83010000000002</v>
@@ -2593,7 +2593,7 @@
         <v>3</v>
       </c>
       <c r="S61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T61" s="1">
         <v>-640.83010000000002</v>
@@ -2614,7 +2614,7 @@
         <v>11</v>
       </c>
       <c r="S62">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -2625,7 +2625,7 @@
         <v>12</v>
       </c>
       <c r="S63">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -2636,7 +2636,7 @@
         <v>13</v>
       </c>
       <c r="S64">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -2647,7 +2647,7 @@
         <v>14</v>
       </c>
       <c r="S65">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -2658,7 +2658,7 @@
         <v>15</v>
       </c>
       <c r="S66">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -2669,7 +2669,7 @@
         <v>16</v>
       </c>
       <c r="S67">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:19">

--- a/TextGame project/Assets/Resources/Story/12.xlsx
+++ b/TextGame project/Assets/Resources/Story/12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4188D1FF-1A03-4D1F-8C85-F94053296ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F849FA08-16BC-49A6-A765-EB23CA059817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -346,6 +346,14 @@
   </si>
   <si>
     <t>（坚定）我会找到你的。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1027,8 +1035,8 @@
       <c r="J3" s="1">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>31</v>
+      <c r="K3" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>67</v>
@@ -1160,8 +1168,8 @@
       <c r="B8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C8" t="s">
-        <v>31</v>
+      <c r="C8" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1264,8 +1272,8 @@
       <c r="B12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C12" t="s">
-        <v>31</v>
+      <c r="C12" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R12">
         <v>8</v>
@@ -1394,8 +1402,8 @@
       <c r="B17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C17" t="s">
-        <v>31</v>
+      <c r="C17" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -1608,8 +1616,8 @@
       <c r="B25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C25" t="s">
-        <v>31</v>
+      <c r="C25" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -1843,8 +1851,8 @@
       <c r="B33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C33" t="s">
-        <v>31</v>
+      <c r="C33" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R33">
         <v>3</v>
@@ -1895,8 +1903,8 @@
       <c r="B35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C35" t="s">
-        <v>31</v>
+      <c r="C35" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R35">
         <v>3</v>
@@ -1947,8 +1955,8 @@
       <c r="B37" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C37" t="s">
-        <v>31</v>
+      <c r="C37" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R37">
         <v>3</v>
@@ -2025,8 +2033,8 @@
       <c r="B40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C40" t="s">
-        <v>31</v>
+      <c r="C40" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R40">
         <v>3</v>
@@ -2161,8 +2169,8 @@
       <c r="B45" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C45" t="s">
-        <v>31</v>
+      <c r="C45" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="R45">
         <v>8</v>
@@ -2400,6 +2408,15 @@
       </c>
       <c r="C54" t="s">
         <v>31</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="R54">
         <v>3</v>
@@ -2683,7 +2700,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A67 A69:A133" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"旁白,千叶,林深,王叔叔,警察"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C5 C7:C151" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C5 C7 C9:C11 C13:C16 C18:C24 C26:C32 C34 C36 C38:C39 C41:C44 C46:C151" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"White,Qianye,Linshen,Wangshushu,Police"</formula1>
     </dataValidation>
   </dataValidations>
